--- a/templates/연차신청서.xlsx
+++ b/templates/연차신청서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준후\Desktop\지산\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준후\Desktop\project\jsec\jsec-fe\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD5927C-0C29-4548-A570-B158DE1D9E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D11E774-9F74-424C-A075-62090988B79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1면" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -681,6 +681,51 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -712,12 +757,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -765,44 +804,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -828,32 +855,47 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,18 +935,6 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -954,264 +984,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>190500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>352425</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1027" name="Check Box 3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1027"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ko-KR" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="굴림"/>
-                  <a:ea typeface="굴림"/>
-                </a:rPr>
-                <a:t>연 차 (반차)</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>666750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>190500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>180975</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1029" name="Check Box 5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1029"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ko-KR" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="굴림"/>
-                  <a:ea typeface="굴림"/>
-                </a:rPr>
-                <a:t>기 타  (                         )</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>190500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>542925</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1025" name="Check Box 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1025"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ko-KR" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="굴림"/>
-                  <a:ea typeface="굴림"/>
-                </a:rPr>
-                <a:t>연 차</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -2105,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:J28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2128,15 +1900,15 @@
       <c r="J1" s="4"/>
     </row>
     <row r="2" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="28" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="41" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -2147,304 +1919,304 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="22"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="37"/>
     </row>
     <row r="4" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="23"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="24"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="48"/>
     </row>
     <row r="7" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="51"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="80"/>
     </row>
     <row r="9" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="54"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="80"/>
     </row>
     <row r="10" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="74"/>
     </row>
     <row r="11" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="77"/>
     </row>
     <row r="12" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="77"/>
     </row>
     <row r="13" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="21"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="77"/>
     </row>
     <row r="15" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="77"/>
     </row>
     <row r="16" spans="2:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="77"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="44"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="47"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="47"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="47"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="45"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="47"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="47"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="47"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="47"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="47"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="47"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" spans="2:10" ht="0.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="48"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="50"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2466,79 +2238,6 @@
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId4" name="Check Box 1">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>190500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>542925</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1027" r:id="rId5" name="Check Box 3">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>190500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>352425</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1029" r:id="rId6" name="Check Box 5">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>666750</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>190500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>180975</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
 </worksheet>
 </file>
 
@@ -2568,15 +2267,15 @@
       <c r="J1" s="4"/>
     </row>
     <row r="2" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="59" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="68" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="12" t="s">
@@ -2587,216 +2286,216 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="22"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="37"/>
     </row>
     <row r="4" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="23"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="24"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="48"/>
     </row>
     <row r="7" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="40"/>
       <c r="G7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="51"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="25"/>
     </row>
     <row r="8" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
     </row>
     <row r="9" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="54"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="62"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="2:10" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="62"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="62"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="62"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="62"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="54"/>
     </row>
     <row r="16" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="62"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="57"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="68"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="60"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="68"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="60"/>
     </row>
     <row r="20" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="69"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="71"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="63"/>
     </row>
     <row r="22" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8"/>
@@ -2811,15 +2510,15 @@
     </row>
     <row r="23" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="59" t="s">
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="68" t="s">
         <v>8</v>
       </c>
       <c r="I24" s="12" t="s">
@@ -2830,219 +2529,231 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="22"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="37"/>
     </row>
     <row r="26" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="57"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="23"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="38"/>
     </row>
     <row r="27" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="57"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="24"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="39"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="35"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="48"/>
     </row>
     <row r="29" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="27"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="25"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="51"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="51"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="54"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="38"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="51"/>
     </row>
     <row r="33" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="62"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="54"/>
     </row>
     <row r="34" spans="2:10" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="62"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="54"/>
     </row>
     <row r="35" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="62"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="54"/>
     </row>
     <row r="36" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="62"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="54"/>
     </row>
     <row r="37" spans="2:10" ht="19.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="62"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" spans="2:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="62"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="54"/>
     </row>
     <row r="39" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="65"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="57"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="66"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="68"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="66"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="68"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="60"/>
     </row>
     <row r="42" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="69"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="71"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="B2:G5"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="C10:J16"/>
+    <mergeCell ref="B17:J20"/>
     <mergeCell ref="B39:J42"/>
     <mergeCell ref="B24:G27"/>
     <mergeCell ref="H24:H27"/>
@@ -3055,18 +2766,6 @@
     <mergeCell ref="B32:B38"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C32:J38"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="C10:J16"/>
-    <mergeCell ref="B17:J20"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="B2:G5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
